--- a/Article_data/Step 3 - PRODCOM data manipulations.xlsx
+++ b/Article_data/Step 3 - PRODCOM data manipulations.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446257C7-A827-451F-A9E9-D43B6D007B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8765A511-2A62-4222-8DC7-669C69194C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-4788" yWindow="-17388" windowWidth="30936" windowHeight="16776" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
-    <sheet name="Filtered Prodcom data" sheetId="3" r:id="rId2"/>
-    <sheet name="Calculations" sheetId="6" r:id="rId3"/>
-    <sheet name="Hotspot products export" sheetId="7" r:id="rId4"/>
-    <sheet name="References" sheetId="5" r:id="rId5"/>
+    <sheet name="Filtered PRODCOM data" sheetId="3" r:id="rId2"/>
+    <sheet name="Correlation EU27 2019-2022" sheetId="8" r:id="rId3"/>
+    <sheet name="Calculations" sheetId="6" r:id="rId4"/>
+    <sheet name="Hotspot products export" sheetId="7" r:id="rId5"/>
+    <sheet name="Sensitivity analysis" sheetId="9" r:id="rId6"/>
+    <sheet name="References" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'Filtered Prodcom data'!$A$4:$AA$239</definedName>
+    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'Filtered PRODCOM data'!$A$4:$AA$239</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -134,7 +136,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -156,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7537" uniqueCount="3100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7844" uniqueCount="3112">
   <si>
     <t>freq</t>
   </si>
@@ -9347,9 +9349,6 @@
     <t>The "In scope" column is filtered to only show rows with no identified issues. The identification process was performed iteratively and manually over the top products in terms of availability (i.e., local production + imports in the EU27). Therefore, only the top 50 products (after filtering) should be considered analyzed by the authors.</t>
   </si>
   <si>
-    <t>Filtered Prodcom data</t>
-  </si>
-  <si>
     <t>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</t>
   </si>
   <si>
@@ -9456,14 +9455,54 @@
   </si>
   <si>
     <t>CN</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Sum of filtered products</t>
+  </si>
+  <si>
+    <t>Pearson coefficient</t>
+  </si>
+  <si>
+    <t>PRODQNT + IMPQNT - EU27 - 2019 (% of sum)</t>
+  </si>
+  <si>
+    <t>PRODQNT + IMPQNT - EU27 - 2022 (% of sum)</t>
+  </si>
+  <si>
+    <t>Pearson correlation EU27 2019 vs 2022</t>
+  </si>
+  <si>
+    <t>Calculate R² correlation coefficient for sensitivity analysis.</t>
+  </si>
+  <si>
+    <t>Refer to SM document for more details</t>
+  </si>
+  <si>
+    <t>Add sensitivity analysis</t>
+  </si>
+  <si>
+    <t>Filtered PRODCOM data</t>
+  </si>
+  <si>
+    <t>Correlation EU27 2019-2022</t>
+  </si>
+  <si>
+    <t>Sensitivity analysis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -9612,7 +9651,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9660,8 +9699,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -9802,6 +9853,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -9824,7 +9901,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="9" applyBorder="1" applyAlignment="1">
@@ -10032,6 +10109,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -10601,7 +10692,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0928EDD3-90ED-405A-8C35-7F6C77CACFAF}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:G49"/>
+  <dimension ref="B2:G53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.77734375" customWidth="1"/>
@@ -10737,277 +10828,307 @@
         <v>46247</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>3071</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="19">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="37">
         <v>46248</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>3080</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="13" t="s">
+      <c r="C25" s="29" t="s">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="19">
+        <v>46251</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="13" t="s">
         <v>2724</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="17" t="s">
+    <row r="30" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="17" t="s">
         <v>2725</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C31" s="18" t="s">
         <v>2713</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="21" t="s">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="21" t="s">
         <v>2726</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C32" s="22" t="s">
         <v>2727</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" s="85" t="s">
-        <v>3063</v>
-      </c>
-      <c r="C32" s="86" t="str">
-        <f>'Filtered Prodcom data'!$B$1</f>
-        <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="85" t="s">
-        <v>2728</v>
+        <v>3109</v>
       </c>
       <c r="C33" s="86" t="str">
+        <f>'Filtered PRODCOM data'!$B$1</f>
+        <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="85" t="s">
+        <v>3110</v>
+      </c>
+      <c r="C34" s="86" t="str">
         <f>Calculations!$B$1</f>
         <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
-        <v>3072</v>
-      </c>
-      <c r="C34" s="86" t="str">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="85" t="s">
+        <v>2728</v>
+      </c>
+      <c r="C35" s="86" t="str">
+        <f>Calculations!$B$1</f>
+        <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="85" t="s">
+        <v>3071</v>
+      </c>
+      <c r="C36" s="86" t="str">
         <f>'Hotspot products export'!$B$1</f>
         <v>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="87" t="s">
+    <row r="37" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="85" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C37" s="86" t="str">
+        <f>'Sensitivity analysis'!$B$1</f>
+        <v>Calculate R² correlation coefficient for sensitivity analysis.</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="87" t="s">
         <v>2729</v>
       </c>
-      <c r="C35" s="88" t="str">
+      <c r="C38" s="88" t="str">
         <f>References!$B$1</f>
         <v>Bibliography: list of references used thoughout the workbook</v>
       </c>
     </row>
-    <row r="37" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="13" t="s">
+    <row r="39" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="106"/>
+      <c r="C39" s="27"/>
+    </row>
+    <row r="41" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="13" t="s">
         <v>2730</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="17" t="s">
+    <row r="43" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B44" s="17" t="s">
         <v>2731</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>2713</v>
       </c>
-      <c r="D40" s="23" t="s">
+      <c r="D44" s="23" t="s">
         <v>2732</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E44" s="23" t="s">
         <v>2733</v>
       </c>
-      <c r="F40" s="23" t="s">
+      <c r="F44" s="23" t="s">
         <v>2734</v>
       </c>
-      <c r="G40" s="24" t="s">
+      <c r="G44" s="24" t="s">
         <v>2735</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="21" t="s">
-        <v>2736</v>
-      </c>
-      <c r="C41" t="s">
-        <v>2737</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>2738</v>
-      </c>
-      <c r="E41" s="25">
-        <v>15</v>
-      </c>
-      <c r="F41" s="25">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G41" s="26">
-        <v>5.5855E-5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="21" t="s">
-        <v>2739</v>
-      </c>
-      <c r="C42" t="s">
-        <v>2740</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>2741</v>
-      </c>
-      <c r="E42" s="3">
-        <v>15</v>
-      </c>
-      <c r="F42" s="3">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G42" s="76">
-        <v>5.5855E-5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="21" t="s">
-        <v>2742</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2743</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>2744</v>
-      </c>
-      <c r="E43" s="4">
-        <v>15</v>
-      </c>
-      <c r="F43" s="68">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G43" s="69">
-        <v>5.5855E-5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B44" s="21" t="s">
-        <v>2745</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2746</v>
-      </c>
-      <c r="D44" s="27" t="s">
-        <v>2747</v>
-      </c>
-      <c r="E44" s="27">
-        <v>15</v>
-      </c>
-      <c r="F44" s="27">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G44" s="28">
-        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="21" t="s">
-        <v>2748</v>
+        <v>2736</v>
       </c>
       <c r="C45" t="s">
-        <v>2749</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>2750</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>2751</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>2752</v>
-      </c>
-      <c r="G45" s="81" t="s">
-        <v>2753</v>
+        <v>2737</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E45" s="25">
+        <v>15</v>
+      </c>
+      <c r="F45" s="25">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G45" s="26">
+        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="21" t="s">
-        <v>2754</v>
+        <v>2739</v>
       </c>
       <c r="C46" t="s">
-        <v>2755</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>2756</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>2757</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>2758</v>
-      </c>
-      <c r="G46" s="73" t="s">
-        <v>2759</v>
+        <v>2740</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15</v>
+      </c>
+      <c r="F46" s="3">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G46" s="76">
+        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="21" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2743</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>2744</v>
+      </c>
+      <c r="E47" s="4">
+        <v>15</v>
+      </c>
+      <c r="F47" s="68">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G47" s="69">
+        <v>5.5855E-5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="21" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E48" s="27">
+        <v>15</v>
+      </c>
+      <c r="F48" s="27">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G48" s="28">
+        <v>5.5855E-5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="21" t="s">
+        <v>2748</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2749</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>2750</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>2751</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>2752</v>
+      </c>
+      <c r="G49" s="81" t="s">
+        <v>2753</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="21" t="s">
+        <v>2754</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2755</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>2756</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>2757</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>2758</v>
+      </c>
+      <c r="G50" s="73" t="s">
+        <v>2759</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="21" t="s">
         <v>2760</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C51" t="s">
         <v>2761</v>
       </c>
-      <c r="D47" s="66" t="s">
+      <c r="D51" s="66" t="s">
         <v>2762</v>
       </c>
-      <c r="E47" s="66" t="s">
+      <c r="E51" s="66" t="s">
         <v>2763</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F51" s="66" t="s">
         <v>2764</v>
       </c>
-      <c r="G47" s="67"/>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="30" t="s">
+      <c r="G51" s="67"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="30" t="s">
         <v>2765</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C52" t="s">
         <v>2766</v>
       </c>
-      <c r="D48" s="31" t="s">
+      <c r="D52" s="31" t="s">
         <v>2767</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E52" s="31">
         <v>15</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F52" s="31">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G52" s="32">
         <v>5.5855E-5</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="33" t="s">
+    <row r="53" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="33" t="s">
         <v>2765</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C53" s="34" t="s">
         <v>2768</v>
       </c>
-      <c r="D49" s="35" t="s">
+      <c r="D53" s="35" t="s">
         <v>2769</v>
       </c>
-      <c r="E49" s="70">
+      <c r="E53" s="70">
         <v>15</v>
       </c>
-      <c r="F49" s="36">
+      <c r="F53" s="36">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G49" s="77">
+      <c r="G53" s="77">
         <v>5.5855E-5</v>
       </c>
     </row>
@@ -11017,10 +11138,12 @@
     <hyperlink ref="C11" r:id="rId2" xr:uid="{41B7F739-267F-43D4-BA81-097B57D6E931}"/>
     <hyperlink ref="C15" r:id="rId3" xr:uid="{A231AF78-61FF-4A68-B4C3-3DDFEB4B0959}"/>
     <hyperlink ref="C14" r:id="rId4" xr:uid="{5739EB44-C6AF-4C59-923B-AEA8B4D6A45E}"/>
-    <hyperlink ref="B32" location="'Filtered Prodcom data'!A1" display="'Filtered Prodcom data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
-    <hyperlink ref="B33" location="'Calculations'!A1" display="'Calculations'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
-    <hyperlink ref="B34" location="'Hotspot products export'!A1" display="'Hotspot products export'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
-    <hyperlink ref="B35" location="'References'!A1" display="'References'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
+    <hyperlink ref="B33" location="'Filtered PRODCOM data'!A1" display="'Filtered PRODCOM data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
+    <hyperlink ref="B34" location="'Correlation EU27 2019-2022'!A1" display="'Correlation EU27 2019-2022'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
+    <hyperlink ref="B35" location="'Calculations'!A1" display="'Calculations'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
+    <hyperlink ref="B36" location="'Hotspot products export'!A1" display="'Hotspot products export'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
+    <hyperlink ref="B37" location="'Sensitivity analysis'!A1" display="'Sensitivity analysis'!A1" xr:uid="{AA5D8B99-4E97-443E-A7C2-70B9BA293EC5}"/>
+    <hyperlink ref="B38" location="'References'!A1" display="'References'!A1" xr:uid="{7C273249-DB68-46C1-9FB7-62B1EF7CFDEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40080,6 +40203,60 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1C0C99-01C6-4D27-A4D9-BFEEB79638BB}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="B3:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="37.77734375" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C3" s="98" t="s">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>704</v>
+      </c>
+      <c r="C4" s="8">
+        <f>SUBTOTAL(9, prodcom_data[PRODQNT + IMPQNT - EU27 - 2019])</f>
+        <v>126375890323</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>705</v>
+      </c>
+      <c r="C5" s="8">
+        <f>SUBTOTAL(9, prodcom_data[PRODQNT + IMPQNT - EU27 - 2022])</f>
+        <v>120083372330</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>3102</v>
+      </c>
+      <c r="C7" s="71" cm="1">
+        <f t="array" ref="C7">PEARSON('Filtered PRODCOM data'!AB6:AB237/'Correlation EU27 2019-2022'!C4, 'Filtered PRODCOM data'!AD6:AD237/'Correlation EU27 2019-2022'!C5)</f>
+        <v>0.99211809005161777</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F69908D-C3FD-4AA4-A1ED-5B5322120E61}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E39"/>
@@ -40095,7 +40272,7 @@
         <v>3058</v>
       </c>
       <c r="B1" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -40116,7 +40293,7 @@
         <v>705</v>
       </c>
       <c r="C6" s="55">
-        <f>'Filtered Prodcom data'!$AD$26</f>
+        <f>'Filtered PRODCOM data'!$AD$26</f>
         <v>2370412440</v>
       </c>
       <c r="D6" s="53" t="s">
@@ -40340,7 +40517,7 @@
         <v>705</v>
       </c>
       <c r="C32" s="55">
-        <f>'Filtered Prodcom data'!AD48</f>
+        <f>'Filtered PRODCOM data'!AD48</f>
         <v>1049281862</v>
       </c>
       <c r="D32" s="53" t="s">
@@ -40406,7 +40583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A13AB6A-DCA0-44FC-B906-F1FE7AA47CE2}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AF115"/>
@@ -40432,7 +40609,7 @@
         <v>3058</v>
       </c>
       <c r="B1" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -40440,41 +40617,41 @@
         <v>3060</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="93" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="94" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="B5" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="6" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="95" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B6" s="50" t="s">
         <v>3078</v>
       </c>
-      <c r="B6" s="50" t="s">
-        <v>3079</v>
-      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="F7" s="98" t="s">
+      <c r="F7" s="99" t="s">
         <v>705</v>
       </c>
-      <c r="G7" s="98"/>
+      <c r="G7" s="99"/>
       <c r="I7" s="47" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="J7" s="47"/>
     </row>
@@ -40504,7 +40681,7 @@
         <v>3056</v>
       </c>
       <c r="I8" s="91" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="J8" s="57" t="s">
         <v>2617</v>
@@ -40567,10 +40744,10 @@
         <v>3053</v>
       </c>
       <c r="AD8" s="57" t="s">
+        <v>3065</v>
+      </c>
+      <c r="AE8" s="57" t="s">
         <v>3066</v>
-      </c>
-      <c r="AE8" s="57" t="s">
-        <v>3067</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
@@ -40640,7 +40817,7 @@
         <v>0.89</v>
       </c>
       <c r="X9" s="59" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="Y9" s="61">
         <f>0.05+0.01</f>
@@ -40730,7 +40907,7 @@
         <v>0.94</v>
       </c>
       <c r="X10" s="59" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="Y10" s="60">
         <v>0.03</v>
@@ -40822,7 +40999,7 @@
         <v>0.97</v>
       </c>
       <c r="X11" s="59" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="Y11" s="60">
         <v>0.01</v>
@@ -40935,7 +41112,7 @@
         <v>111</v>
       </c>
       <c r="C13" s="89" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
@@ -41185,7 +41362,7 @@
         <v>0.92</v>
       </c>
       <c r="X15" s="59" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="Y15" s="61">
         <f>0.03+0.03</f>
@@ -41440,7 +41617,7 @@
         <v>0.06</v>
       </c>
       <c r="Z18" s="59" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="AA18" s="60">
         <v>0.03</v>
@@ -42801,7 +42978,7 @@
         <v>0.98</v>
       </c>
       <c r="X35" s="59" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="Y35" s="60">
         <v>0.01</v>
@@ -44528,7 +44705,7 @@
         <v>62</v>
       </c>
       <c r="E57" s="48" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="F57" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B57, prodcom_data[product], 0))</f>
@@ -44543,13 +44720,13 @@
         <v>0.99702850277831634</v>
       </c>
       <c r="I57" s="49" t="s">
+        <v>3085</v>
+      </c>
+      <c r="J57" s="49" t="s">
         <v>3086</v>
       </c>
-      <c r="J57" s="49" t="s">
+      <c r="K57" s="79" t="s">
         <v>3087</v>
-      </c>
-      <c r="K57" s="79" t="s">
-        <v>3088</v>
       </c>
       <c r="L57" s="79">
         <v>50.49</v>
@@ -44562,7 +44739,7 @@
         <v>0.23788869082986727</v>
       </c>
       <c r="O57" s="81" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="P57" s="59" t="s">
         <v>3036</v>
@@ -44604,7 +44781,7 @@
         <v>394</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="F58" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B58, prodcom_data[product], 0))</f>
@@ -44623,7 +44800,7 @@
       </c>
       <c r="J58" s="49"/>
       <c r="K58" s="79" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="L58" s="79">
         <v>72.11</v>
@@ -44636,7 +44813,7 @@
         <v>0.66625988073776177</v>
       </c>
       <c r="O58" s="81" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="P58" s="59" t="s">
         <v>3042</v>
@@ -44678,7 +44855,7 @@
         <v>165</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="F59" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B59, prodcom_data[product], 0))</f>
@@ -44693,11 +44870,11 @@
         <v>0.77509698342872879</v>
       </c>
       <c r="I59" s="49" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="J59" s="49"/>
       <c r="K59" s="79" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="L59" s="79">
         <v>228.29</v>
@@ -44710,7 +44887,7 @@
         <v>0.78919356958254849</v>
       </c>
       <c r="O59" s="81" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="P59" s="59" t="s">
         <v>3036</v>
@@ -44861,11 +45038,11 @@
         <v>1.1148601794389756E-2</v>
       </c>
       <c r="I61" s="49" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="J61" s="49"/>
       <c r="K61" s="79" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="L61" s="79">
         <v>102.09</v>
@@ -44878,7 +45055,7 @@
         <v>0.47060436869428929</v>
       </c>
       <c r="O61" s="81" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="P61" s="59" t="s">
         <v>3042</v>
@@ -45261,7 +45438,3572 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5218DADF-14EE-46ED-AB80-15A77CD37A67}">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:I149"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="50"/>
+    <col min="2" max="2" width="41.21875" style="50" customWidth="1"/>
+    <col min="3" max="4" width="33.6640625" style="50" customWidth="1"/>
+    <col min="5" max="6" width="14.88671875" style="50" customWidth="1"/>
+    <col min="7" max="7" width="12" style="50" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.6640625" style="50" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="50" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="100" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="100" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="100" t="s">
+        <v>704</v>
+      </c>
+      <c r="D4" s="100" t="s">
+        <v>705</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>3103</v>
+      </c>
+      <c r="F4" s="100" t="s">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>614</v>
+      </c>
+      <c r="B5" s="101" t="s">
+        <v>615</v>
+      </c>
+      <c r="C5" s="103" cm="1">
+        <f t="array" aca="1" ref="C5:C147" ca="1">_xlfn.LET(_xlpm.x, 'Filtered PRODCOM data'!AB6:AB237, _xlfn._xlws.FILTER(_xlpm.x,SUBTOTAL(103,OFFSET(_xlpm.x,_xlfn.SEQUENCE(ROWS(_xlpm.x))-1,0,1))))</f>
+        <v>11040770827</v>
+      </c>
+      <c r="D5" s="103" cm="1">
+        <f t="array" aca="1" ref="D5:D147" ca="1">_xlfn.LET(_xlpm.x, 'Filtered PRODCOM data'!AD6:AD237, _xlfn._xlws.FILTER(_xlpm.x,SUBTOTAL(103,OFFSET(_xlpm.x,_xlfn.SEQUENCE(ROWS(_xlpm.x))-1,0,1))))</f>
+        <v>11059816493</v>
+      </c>
+      <c r="E5" s="104">
+        <f ca="1">C5/C$149</f>
+        <v>8.7364534475533703E-2</v>
+      </c>
+      <c r="F5" s="104">
+        <f ca="1">D5/D$149</f>
+        <v>9.2101148380531989E-2</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5" s="50" t="s">
+        <v>3105</v>
+      </c>
+      <c r="I5" s="105">
+        <f ca="1">PEARSON(E5:E147, F5:F147)</f>
+        <v>0.99350674883878221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="102" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="102" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="103">
+        <f ca="1"/>
+        <v>11236268617</v>
+      </c>
+      <c r="D6" s="103">
+        <f ca="1"/>
+        <v>10337493766</v>
+      </c>
+      <c r="E6" s="104">
+        <f t="shared" ref="E6:F69" ca="1" si="0">C6/C$149</f>
+        <v>8.891148927443035E-2</v>
+      </c>
+      <c r="F6" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>8.6085971483142801E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="103">
+        <f ca="1"/>
+        <v>10638016027</v>
+      </c>
+      <c r="D7" s="103">
+        <f ca="1"/>
+        <v>9081741202</v>
+      </c>
+      <c r="E7" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>8.4177575325567577E-2</v>
+      </c>
+      <c r="F7" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.5628632222640713E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="102" t="s">
+        <v>539</v>
+      </c>
+      <c r="B8" s="102" t="s">
+        <v>540</v>
+      </c>
+      <c r="C8" s="103">
+        <f ca="1"/>
+        <v>7504219963</v>
+      </c>
+      <c r="D8" s="103">
+        <f ca="1"/>
+        <v>7628879471</v>
+      </c>
+      <c r="E8" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.9380155058217275E-2</v>
+      </c>
+      <c r="F8" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.3529856989984812E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="101" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="103">
+        <f ca="1"/>
+        <v>7704716635</v>
+      </c>
+      <c r="D9" s="103">
+        <f ca="1"/>
+        <v>6904732058</v>
+      </c>
+      <c r="E9" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.0966665519093612E-2</v>
+      </c>
+      <c r="F9" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.749948493306109E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="102" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="102" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="103">
+        <f ca="1"/>
+        <v>6436740843</v>
+      </c>
+      <c r="D10" s="103">
+        <f ca="1"/>
+        <v>6234476067</v>
+      </c>
+      <c r="E10" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.0933297692689207E-2</v>
+      </c>
+      <c r="F10" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.1917896258501919E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="101" t="s">
+        <v>563</v>
+      </c>
+      <c r="B11" s="101" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" s="103">
+        <f ca="1"/>
+        <v>5458423542</v>
+      </c>
+      <c r="D11" s="103">
+        <f ca="1"/>
+        <v>5008047468</v>
+      </c>
+      <c r="E11" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.3191969038152721E-2</v>
+      </c>
+      <c r="F11" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.1704753712590879E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="102" t="s">
+        <v>536</v>
+      </c>
+      <c r="B12" s="102" t="s">
+        <v>537</v>
+      </c>
+      <c r="C12" s="103">
+        <f ca="1"/>
+        <v>4651264479</v>
+      </c>
+      <c r="D12" s="103">
+        <f ca="1"/>
+        <v>4474213876</v>
+      </c>
+      <c r="E12" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.6804998699609438E-2</v>
+      </c>
+      <c r="F12" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.7259229060493525E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="101" t="s">
+        <v>533</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>534</v>
+      </c>
+      <c r="C13" s="103">
+        <f ca="1"/>
+        <v>2630915453</v>
+      </c>
+      <c r="D13" s="103">
+        <f ca="1"/>
+        <v>4238710053</v>
+      </c>
+      <c r="E13" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.0818175415229356E-2</v>
+      </c>
+      <c r="F13" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.5298059762609267E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="102" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="103">
+        <f ca="1"/>
+        <v>3661349747</v>
+      </c>
+      <c r="D14" s="103">
+        <f ca="1"/>
+        <v>3627976392</v>
+      </c>
+      <c r="E14" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.8971900713356608E-2</v>
+      </c>
+      <c r="F14" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.0212146124860582E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="101" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="101" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15" s="103">
+        <f ca="1"/>
+        <v>3991929739</v>
+      </c>
+      <c r="D15" s="103">
+        <f ca="1"/>
+        <v>3491283735</v>
+      </c>
+      <c r="E15" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.1587747700903689E-2</v>
+      </c>
+      <c r="F15" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.9073831516037339E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="102" t="s">
+        <v>599</v>
+      </c>
+      <c r="B16" s="102" t="s">
+        <v>600</v>
+      </c>
+      <c r="C16" s="103">
+        <f ca="1"/>
+        <v>3608586975</v>
+      </c>
+      <c r="D16" s="103">
+        <f ca="1"/>
+        <v>3349184970</v>
+      </c>
+      <c r="E16" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.8554394084005508E-2</v>
+      </c>
+      <c r="F16" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.7890497285470429E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="103">
+        <f ca="1"/>
+        <v>2770747674</v>
+      </c>
+      <c r="D17" s="103">
+        <f ca="1"/>
+        <v>2808940257</v>
+      </c>
+      <c r="E17" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.1924654037398565E-2</v>
+      </c>
+      <c r="F17" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.3391583718025317E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="102" t="s">
+        <v>634</v>
+      </c>
+      <c r="B18" s="102" t="s">
+        <v>635</v>
+      </c>
+      <c r="C18" s="103">
+        <f ca="1"/>
+        <v>2102028618</v>
+      </c>
+      <c r="D18" s="103">
+        <f ca="1"/>
+        <v>2370412440</v>
+      </c>
+      <c r="E18" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.6633145868468216E-2</v>
+      </c>
+      <c r="F18" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.9739722444552035E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="101" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="103">
+        <f ca="1"/>
+        <v>1674679674</v>
+      </c>
+      <c r="D19" s="103">
+        <f ca="1"/>
+        <v>2000046666</v>
+      </c>
+      <c r="E19" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3251575674123767E-2</v>
+      </c>
+      <c r="F19" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.6655483829215674E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="102" t="s">
+        <v>548</v>
+      </c>
+      <c r="B20" s="102" t="s">
+        <v>549</v>
+      </c>
+      <c r="C20" s="103">
+        <f ca="1"/>
+        <v>1746705493</v>
+      </c>
+      <c r="D20" s="103">
+        <f ca="1"/>
+        <v>1864065177</v>
+      </c>
+      <c r="E20" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3821508901228333E-2</v>
+      </c>
+      <c r="F20" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.5523091505769674E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="101" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="101" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="103">
+        <f ca="1"/>
+        <v>1922839638</v>
+      </c>
+      <c r="D21" s="103">
+        <f ca="1"/>
+        <v>1795747967</v>
+      </c>
+      <c r="E21" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.5215241080284199E-2</v>
+      </c>
+      <c r="F21" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.4954176687053072E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="102" t="s">
+        <v>476</v>
+      </c>
+      <c r="B22" s="102" t="s">
+        <v>477</v>
+      </c>
+      <c r="C22" s="103">
+        <f ca="1"/>
+        <v>1712772337</v>
+      </c>
+      <c r="D22" s="103">
+        <f ca="1"/>
+        <v>1650938177</v>
+      </c>
+      <c r="E22" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3552999172724966E-2</v>
+      </c>
+      <c r="F22" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3748266266732352E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="101" t="s">
+        <v>551</v>
+      </c>
+      <c r="B23" s="101" t="s">
+        <v>552</v>
+      </c>
+      <c r="C23" s="103">
+        <f ca="1"/>
+        <v>1937142969</v>
+      </c>
+      <c r="D23" s="103">
+        <f ca="1"/>
+        <v>1592476459</v>
+      </c>
+      <c r="E23" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.5328421932766761E-2</v>
+      </c>
+      <c r="F23" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3261423526845418E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="102" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="103">
+        <f ca="1"/>
+        <v>1418388518</v>
+      </c>
+      <c r="D24" s="103">
+        <f ca="1"/>
+        <v>1202939382</v>
+      </c>
+      <c r="E24" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.1223568944794669E-2</v>
+      </c>
+      <c r="F24" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.0017534973070322E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="101" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="101" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="103">
+        <f ca="1"/>
+        <v>1361980725</v>
+      </c>
+      <c r="D25" s="103">
+        <f ca="1"/>
+        <v>1191905947</v>
+      </c>
+      <c r="E25" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.0777219622500448E-2</v>
+      </c>
+      <c r="F25" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.9256535178287152E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="102" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="102" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="103">
+        <f ca="1"/>
+        <v>1329892936</v>
+      </c>
+      <c r="D26" s="103">
+        <f ca="1"/>
+        <v>1120381615</v>
+      </c>
+      <c r="E26" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.0523312101706822E-2</v>
+      </c>
+      <c r="F26" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.3300312379726458E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="101" t="s">
+        <v>420</v>
+      </c>
+      <c r="B27" s="101" t="s">
+        <v>421</v>
+      </c>
+      <c r="C27" s="103">
+        <f ca="1"/>
+        <v>1391723012</v>
+      </c>
+      <c r="D27" s="103">
+        <f ca="1"/>
+        <v>1090852807</v>
+      </c>
+      <c r="E27" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.1012567416482216E-2</v>
+      </c>
+      <c r="F27" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.0841286835469399E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="102" t="s">
+        <v>345</v>
+      </c>
+      <c r="B28" s="102" t="s">
+        <v>346</v>
+      </c>
+      <c r="C28" s="103">
+        <f ca="1"/>
+        <v>1166925937</v>
+      </c>
+      <c r="D28" s="103">
+        <f ca="1"/>
+        <v>1049281862</v>
+      </c>
+      <c r="E28" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.2337702548919119E-3</v>
+      </c>
+      <c r="F28" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>8.7379446599524062E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="101" t="s">
+        <v>387</v>
+      </c>
+      <c r="B29" s="101" t="s">
+        <v>388</v>
+      </c>
+      <c r="C29" s="103">
+        <f ca="1"/>
+        <v>1011227633</v>
+      </c>
+      <c r="D29" s="103">
+        <f ca="1"/>
+        <v>931200527</v>
+      </c>
+      <c r="E29" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>8.0017448772502133E-3</v>
+      </c>
+      <c r="F29" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.7546167211308527E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="102" t="s">
+        <v>620</v>
+      </c>
+      <c r="B30" s="102" t="s">
+        <v>621</v>
+      </c>
+      <c r="C30" s="103">
+        <f ca="1"/>
+        <v>1083844066</v>
+      </c>
+      <c r="D30" s="103">
+        <f ca="1"/>
+        <v>914892768</v>
+      </c>
+      <c r="E30" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>8.5763515748916858E-3</v>
+      </c>
+      <c r="F30" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.6188130816795489E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="101" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="101" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="103">
+        <f ca="1"/>
+        <v>1257675114</v>
+      </c>
+      <c r="D31" s="103">
+        <f ca="1"/>
+        <v>888564975</v>
+      </c>
+      <c r="E31" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.9518595737331655E-3</v>
+      </c>
+      <c r="F31" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.3995671320600731E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="102" t="s">
+        <v>473</v>
+      </c>
+      <c r="B32" s="102" t="s">
+        <v>474</v>
+      </c>
+      <c r="C32" s="103">
+        <f ca="1"/>
+        <v>958122685</v>
+      </c>
+      <c r="D32" s="103">
+        <f ca="1"/>
+        <v>886759378</v>
+      </c>
+      <c r="E32" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.5815306428399084E-3</v>
+      </c>
+      <c r="F32" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.3845309370818204E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="101" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="103">
+        <f ca="1"/>
+        <v>914404936</v>
+      </c>
+      <c r="D33" s="103">
+        <f ca="1"/>
+        <v>882272543</v>
+      </c>
+      <c r="E33" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.2355963915498624E-3</v>
+      </c>
+      <c r="F33" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.3471666050103504E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="102" t="s">
+        <v>293</v>
+      </c>
+      <c r="B34" s="102" t="s">
+        <v>294</v>
+      </c>
+      <c r="C34" s="103">
+        <f ca="1"/>
+        <v>935192179</v>
+      </c>
+      <c r="D34" s="103">
+        <f ca="1"/>
+        <v>881884158</v>
+      </c>
+      <c r="E34" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.40008380245451E-3</v>
+      </c>
+      <c r="F34" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.3439323104326415E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="101" t="s">
+        <v>602</v>
+      </c>
+      <c r="B35" s="101" t="s">
+        <v>603</v>
+      </c>
+      <c r="C35" s="103">
+        <f ca="1"/>
+        <v>705247106</v>
+      </c>
+      <c r="D35" s="103">
+        <f ca="1"/>
+        <v>872335906</v>
+      </c>
+      <c r="E35" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.5805510386315142E-3</v>
+      </c>
+      <c r="F35" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.2644187873300379E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="102" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" s="102" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" s="103">
+        <f ca="1"/>
+        <v>718906452</v>
+      </c>
+      <c r="D36" s="103">
+        <f ca="1"/>
+        <v>848026699</v>
+      </c>
+      <c r="E36" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.6886361010994304E-3</v>
+      </c>
+      <c r="F36" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.0619827087262813E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="101" t="s">
+        <v>557</v>
+      </c>
+      <c r="B37" s="101" t="s">
+        <v>558</v>
+      </c>
+      <c r="C37" s="103">
+        <f ca="1"/>
+        <v>935915365</v>
+      </c>
+      <c r="D37" s="103">
+        <f ca="1"/>
+        <v>846217183</v>
+      </c>
+      <c r="E37" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.4058063021983428E-3</v>
+      </c>
+      <c r="F37" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.0469138780889532E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="102" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="103">
+        <f ca="1"/>
+        <v>969703945</v>
+      </c>
+      <c r="D38" s="103">
+        <f ca="1"/>
+        <v>821433537</v>
+      </c>
+      <c r="E38" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.673172015022529E-3</v>
+      </c>
+      <c r="F38" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.8405268861256342E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="101" t="s">
+        <v>569</v>
+      </c>
+      <c r="B39" s="101" t="s">
+        <v>570</v>
+      </c>
+      <c r="C39" s="103">
+        <f ca="1"/>
+        <v>796666774</v>
+      </c>
+      <c r="D39" s="103">
+        <f ca="1"/>
+        <v>790721030</v>
+      </c>
+      <c r="E39" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.3039458868604245E-3</v>
+      </c>
+      <c r="F39" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.5847670219239584E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="102" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="102" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="103">
+        <f ca="1"/>
+        <v>1358034437</v>
+      </c>
+      <c r="D40" s="103">
+        <f ca="1"/>
+        <v>778495527</v>
+      </c>
+      <c r="E40" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.0745993033394616E-2</v>
+      </c>
+      <c r="F40" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.4829585636604512E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="101" t="s">
+        <v>332</v>
+      </c>
+      <c r="B41" s="101" t="s">
+        <v>333</v>
+      </c>
+      <c r="C41" s="103">
+        <f ca="1"/>
+        <v>672193341</v>
+      </c>
+      <c r="D41" s="103">
+        <f ca="1"/>
+        <v>705069102</v>
+      </c>
+      <c r="E41" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.3189998446852719E-3</v>
+      </c>
+      <c r="F41" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.8714965137921524E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="102" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="102" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="103">
+        <f ca="1"/>
+        <v>1071520507</v>
+      </c>
+      <c r="D42" s="103">
+        <f ca="1"/>
+        <v>683315016</v>
+      </c>
+      <c r="E42" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>8.4788364636746438E-3</v>
+      </c>
+      <c r="F42" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.6903383269599423E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="101" t="s">
+        <v>252</v>
+      </c>
+      <c r="B43" s="101" t="s">
+        <v>253</v>
+      </c>
+      <c r="C43" s="103">
+        <f ca="1"/>
+        <v>467809488</v>
+      </c>
+      <c r="D43" s="103">
+        <f ca="1"/>
+        <v>667655569</v>
+      </c>
+      <c r="E43" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.7017305025851136E-3</v>
+      </c>
+      <c r="F43" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.5599335365534366E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="102" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="102" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="103">
+        <f ca="1"/>
+        <v>439330226</v>
+      </c>
+      <c r="D44" s="103">
+        <f ca="1"/>
+        <v>667347651</v>
+      </c>
+      <c r="E44" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.4763769012992134E-3</v>
+      </c>
+      <c r="F44" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.5573693347490951E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="101" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="101" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="103">
+        <f ca="1"/>
+        <v>739663058</v>
+      </c>
+      <c r="D45" s="103">
+        <f ca="1"/>
+        <v>642497260</v>
+      </c>
+      <c r="E45" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.8528810844340595E-3</v>
+      </c>
+      <c r="F45" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.3504265206206839E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="102" t="s">
+        <v>220</v>
+      </c>
+      <c r="B46" s="102" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" s="103">
+        <f ca="1"/>
+        <v>778454260</v>
+      </c>
+      <c r="D46" s="103">
+        <f ca="1"/>
+        <v>604861873</v>
+      </c>
+      <c r="E46" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>6.1598320534903793E-3</v>
+      </c>
+      <c r="F46" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.0370160436349568E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="101" t="s">
+        <v>542</v>
+      </c>
+      <c r="B47" s="101" t="s">
+        <v>543</v>
+      </c>
+      <c r="C47" s="103">
+        <f ca="1"/>
+        <v>683098155</v>
+      </c>
+      <c r="D47" s="103">
+        <f ca="1"/>
+        <v>593659673</v>
+      </c>
+      <c r="E47" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.4052885661504879E-3</v>
+      </c>
+      <c r="F47" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.9437291898212967E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="102" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="102" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="103">
+        <f ca="1"/>
+        <v>401394035</v>
+      </c>
+      <c r="D48" s="103">
+        <f ca="1"/>
+        <v>507331541</v>
+      </c>
+      <c r="E48" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.1761915502560665E-3</v>
+      </c>
+      <c r="F48" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.2248275606868108E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="101" t="s">
+        <v>284</v>
+      </c>
+      <c r="B49" s="101" t="s">
+        <v>285</v>
+      </c>
+      <c r="C49" s="103">
+        <f ca="1"/>
+        <v>689068394</v>
+      </c>
+      <c r="D49" s="103">
+        <f ca="1"/>
+        <v>443739559</v>
+      </c>
+      <c r="E49" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>5.4525304806069628E-3</v>
+      </c>
+      <c r="F49" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.6952623030985792E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="102" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="102" t="s">
+        <v>187</v>
+      </c>
+      <c r="C50" s="103">
+        <f ca="1"/>
+        <v>383703984</v>
+      </c>
+      <c r="D50" s="103">
+        <f ca="1"/>
+        <v>377601386</v>
+      </c>
+      <c r="E50" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.0362119152577563E-3</v>
+      </c>
+      <c r="F50" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.1444935187389402E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="101" t="s">
+        <v>581</v>
+      </c>
+      <c r="B51" s="101" t="s">
+        <v>582</v>
+      </c>
+      <c r="C51" s="103">
+        <f ca="1"/>
+        <v>275890259</v>
+      </c>
+      <c r="D51" s="103">
+        <f ca="1"/>
+        <v>334412816</v>
+      </c>
+      <c r="E51" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.1830925051832366E-3</v>
+      </c>
+      <c r="F51" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.7848386459451125E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="102" t="s">
+        <v>459</v>
+      </c>
+      <c r="B52" s="102" t="s">
+        <v>460</v>
+      </c>
+      <c r="C52" s="103">
+        <f ca="1"/>
+        <v>378364331</v>
+      </c>
+      <c r="D52" s="103">
+        <f ca="1"/>
+        <v>321846701</v>
+      </c>
+      <c r="E52" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.9939597658457718E-3</v>
+      </c>
+      <c r="F52" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.6801937250357697E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="101" t="s">
+        <v>226</v>
+      </c>
+      <c r="B53" s="101" t="s">
+        <v>227</v>
+      </c>
+      <c r="C53" s="103">
+        <f ca="1"/>
+        <v>452919443</v>
+      </c>
+      <c r="D53" s="103">
+        <f ca="1"/>
+        <v>321638245</v>
+      </c>
+      <c r="E53" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.5839070398823543E-3</v>
+      </c>
+      <c r="F53" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.6784577977716092E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="103">
+        <f ca="1"/>
+        <v>343130144</v>
+      </c>
+      <c r="D54" s="103">
+        <f ca="1"/>
+        <v>318208407</v>
+      </c>
+      <c r="E54" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.7151551069037371E-3</v>
+      </c>
+      <c r="F54" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.6498956585390893E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="101" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="101" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="103">
+        <f ca="1"/>
+        <v>215877794</v>
+      </c>
+      <c r="D55" s="103">
+        <f ca="1"/>
+        <v>300894106</v>
+      </c>
+      <c r="E55" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.7082197676174229E-3</v>
+      </c>
+      <c r="F55" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.5057099926633947E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="102" t="s">
+        <v>393</v>
+      </c>
+      <c r="B56" s="102" t="s">
+        <v>394</v>
+      </c>
+      <c r="C56" s="103">
+        <f ca="1"/>
+        <v>560332007</v>
+      </c>
+      <c r="D56" s="103">
+        <f ca="1"/>
+        <v>300000000</v>
+      </c>
+      <c r="E56" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.4338521023896708E-3</v>
+      </c>
+      <c r="F56" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.4982642823818506E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="101" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="101" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" s="103">
+        <f ca="1"/>
+        <v>348361171</v>
+      </c>
+      <c r="D57" s="103">
+        <f ca="1"/>
+        <v>258032226</v>
+      </c>
+      <c r="E57" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.7565477094534021E-3</v>
+      </c>
+      <c r="F57" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.1487756463976046E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="102" t="s">
+        <v>623</v>
+      </c>
+      <c r="B58" s="102" t="s">
+        <v>624</v>
+      </c>
+      <c r="C58" s="103">
+        <f ca="1"/>
+        <v>246609390</v>
+      </c>
+      <c r="D58" s="103">
+        <f ca="1"/>
+        <v>250743096</v>
+      </c>
+      <c r="E58" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.9513958664876595E-3</v>
+      </c>
+      <c r="F58" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.0880750693021448E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="101" t="s">
+        <v>208</v>
+      </c>
+      <c r="B59" s="101" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="103">
+        <f ca="1"/>
+        <v>230358293</v>
+      </c>
+      <c r="D59" s="103">
+        <f ca="1"/>
+        <v>215273632</v>
+      </c>
+      <c r="E59" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.8228025330720501E-3</v>
+      </c>
+      <c r="F59" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.7927014192140485E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="102" t="s">
+        <v>676</v>
+      </c>
+      <c r="B60" s="102" t="s">
+        <v>677</v>
+      </c>
+      <c r="C60" s="103">
+        <f ca="1"/>
+        <v>173966767</v>
+      </c>
+      <c r="D60" s="103">
+        <f ca="1"/>
+        <v>215072005</v>
+      </c>
+      <c r="E60" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3765819299501197E-3</v>
+      </c>
+      <c r="F60" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.7910223607725026E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="101" t="s">
+        <v>674</v>
+      </c>
+      <c r="B61" s="101" t="s">
+        <v>675</v>
+      </c>
+      <c r="C61" s="103">
+        <f ca="1"/>
+        <v>120666257</v>
+      </c>
+      <c r="D61" s="103">
+        <f ca="1"/>
+        <v>199361212</v>
+      </c>
+      <c r="E61" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.5482023265349954E-4</v>
+      </c>
+      <c r="F61" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.6601899841065199E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="102" t="s">
+        <v>554</v>
+      </c>
+      <c r="B62" s="102" t="s">
+        <v>555</v>
+      </c>
+      <c r="C62" s="103">
+        <f ca="1"/>
+        <v>257947893</v>
+      </c>
+      <c r="D62" s="103">
+        <f ca="1"/>
+        <v>192897948</v>
+      </c>
+      <c r="E62" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.0411163263872518E-3</v>
+      </c>
+      <c r="F62" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.6063668454438383E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="101" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" s="101" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="103">
+        <f ca="1"/>
+        <v>239943672</v>
+      </c>
+      <c r="D63" s="103">
+        <f ca="1"/>
+        <v>191832537</v>
+      </c>
+      <c r="E63" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.8986506950553293E-3</v>
+      </c>
+      <c r="F63" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.5974945846193159E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="102" t="s">
+        <v>608</v>
+      </c>
+      <c r="B64" s="102" t="s">
+        <v>609</v>
+      </c>
+      <c r="C64" s="103">
+        <f ca="1"/>
+        <v>173467538</v>
+      </c>
+      <c r="D64" s="103">
+        <f ca="1"/>
+        <v>184664437</v>
+      </c>
+      <c r="E64" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3726315799369641E-3</v>
+      </c>
+      <c r="F64" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.5378018906108447E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="101" t="s">
+        <v>232</v>
+      </c>
+      <c r="B65" s="101" t="s">
+        <v>233</v>
+      </c>
+      <c r="C65" s="103">
+        <f ca="1"/>
+        <v>187133380</v>
+      </c>
+      <c r="D65" s="103">
+        <f ca="1"/>
+        <v>178851124</v>
+      </c>
+      <c r="E65" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.4807680446144588E-3</v>
+      </c>
+      <c r="F65" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.4893912498434912E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="102" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" s="102" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" s="103">
+        <f ca="1"/>
+        <v>163513061</v>
+      </c>
+      <c r="D66" s="103">
+        <f ca="1"/>
+        <v>175733411</v>
+      </c>
+      <c r="E66" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.2938627817543546E-3</v>
+      </c>
+      <c r="F66" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.4634283464080992E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="101" t="s">
+        <v>669</v>
+      </c>
+      <c r="B67" s="101" t="s">
+        <v>670</v>
+      </c>
+      <c r="C67" s="103">
+        <f ca="1"/>
+        <v>140197294</v>
+      </c>
+      <c r="D67" s="103">
+        <f ca="1"/>
+        <v>161101341</v>
+      </c>
+      <c r="E67" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.1093674089391128E-3</v>
+      </c>
+      <c r="F67" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.341579086880396E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="102" t="s">
+        <v>423</v>
+      </c>
+      <c r="B68" s="102" t="s">
+        <v>424</v>
+      </c>
+      <c r="C68" s="103">
+        <f ca="1"/>
+        <v>172724696</v>
+      </c>
+      <c r="D68" s="103">
+        <f ca="1"/>
+        <v>157621582</v>
+      </c>
+      <c r="E68" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3667535441969081E-3</v>
+      </c>
+      <c r="F68" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3126012281437401E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="101" t="s">
+        <v>177</v>
+      </c>
+      <c r="B69" s="101" t="s">
+        <v>178</v>
+      </c>
+      <c r="C69" s="103">
+        <f ca="1"/>
+        <v>178932241</v>
+      </c>
+      <c r="D69" s="103">
+        <f ca="1"/>
+        <v>146947489</v>
+      </c>
+      <c r="E69" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.4158732377091306E-3</v>
+      </c>
+      <c r="F69" s="104">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.2237122105146661E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="102" t="s">
+        <v>174</v>
+      </c>
+      <c r="B70" s="102" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" s="103">
+        <f ca="1"/>
+        <v>178027001</v>
+      </c>
+      <c r="D70" s="103">
+        <f ca="1"/>
+        <v>144173007</v>
+      </c>
+      <c r="E70" s="104">
+        <f t="shared" ref="E70:F133" ca="1" si="1">C70/C$149</f>
+        <v>1.4087101625554258E-3</v>
+      </c>
+      <c r="F70" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2006075795722949E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="103">
+        <f ca="1"/>
+        <v>123226171</v>
+      </c>
+      <c r="D71" s="103">
+        <f ca="1"/>
+        <v>143056485</v>
+      </c>
+      <c r="E71" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.7507658054910842E-4</v>
+      </c>
+      <c r="F71" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1913096894619832E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="102" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" s="102" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72" s="103">
+        <f ca="1"/>
+        <v>216307198</v>
+      </c>
+      <c r="D72" s="103">
+        <f ca="1"/>
+        <v>131264959</v>
+      </c>
+      <c r="E72" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.7116175992679262E-3</v>
+      </c>
+      <c r="F72" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0931151953267268E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="101" t="s">
+        <v>305</v>
+      </c>
+      <c r="B73" s="101" t="s">
+        <v>306</v>
+      </c>
+      <c r="C73" s="103">
+        <f ca="1"/>
+        <v>183679653</v>
+      </c>
+      <c r="D73" s="103">
+        <f ca="1"/>
+        <v>129400775</v>
+      </c>
+      <c r="E73" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4534390422931082E-3</v>
+      </c>
+      <c r="F73" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0775911143167676E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="102" t="s">
+        <v>628</v>
+      </c>
+      <c r="B74" s="102" t="s">
+        <v>629</v>
+      </c>
+      <c r="C74" s="103">
+        <f ca="1"/>
+        <v>125944781</v>
+      </c>
+      <c r="D74" s="103">
+        <f ca="1"/>
+        <v>124425211</v>
+      </c>
+      <c r="E74" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.9658867429619578E-4</v>
+      </c>
+      <c r="F74" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0361568682304178E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="101" t="s">
+        <v>575</v>
+      </c>
+      <c r="B75" s="101" t="s">
+        <v>576</v>
+      </c>
+      <c r="C75" s="103">
+        <f ca="1"/>
+        <v>181010365</v>
+      </c>
+      <c r="D75" s="103">
+        <f ca="1"/>
+        <v>123148493</v>
+      </c>
+      <c r="E75" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4323172286846925E-3</v>
+      </c>
+      <c r="F75" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0255249383035044E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="102" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="102" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" s="103">
+        <f ca="1"/>
+        <v>109316549</v>
+      </c>
+      <c r="D76" s="103">
+        <f ca="1"/>
+        <v>122962437</v>
+      </c>
+      <c r="E76" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.6501110869012608E-4</v>
+      </c>
+      <c r="F76" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0239755481057616E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="101" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" s="101" t="s">
+        <v>230</v>
+      </c>
+      <c r="C77" s="103">
+        <f ca="1"/>
+        <v>46338989</v>
+      </c>
+      <c r="D77" s="103">
+        <f ca="1"/>
+        <v>119555866</v>
+      </c>
+      <c r="E77" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.6667586579658266E-4</v>
+      </c>
+      <c r="F77" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.956071659234355E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="102" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" s="102" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" s="103">
+        <f ca="1"/>
+        <v>53744269</v>
+      </c>
+      <c r="D78" s="103">
+        <f ca="1"/>
+        <v>109553337</v>
+      </c>
+      <c r="E78" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.2527311865132487E-4</v>
+      </c>
+      <c r="F78" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.123106294761401E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="101" t="s">
+        <v>381</v>
+      </c>
+      <c r="B79" s="101" t="s">
+        <v>382</v>
+      </c>
+      <c r="C79" s="103">
+        <f ca="1"/>
+        <v>146392934</v>
+      </c>
+      <c r="D79" s="103">
+        <f ca="1"/>
+        <v>108792952</v>
+      </c>
+      <c r="E79" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1583928993563494E-3</v>
+      </c>
+      <c r="F79" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.0597848718827702E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="102" t="s">
+        <v>449</v>
+      </c>
+      <c r="B80" s="102" t="s">
+        <v>450</v>
+      </c>
+      <c r="C80" s="103">
+        <f ca="1"/>
+        <v>133694804</v>
+      </c>
+      <c r="D80" s="103">
+        <f ca="1"/>
+        <v>108478131</v>
+      </c>
+      <c r="E80" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0579138446288594E-3</v>
+      </c>
+      <c r="F80" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.0335680032279785E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="101" t="s">
+        <v>287</v>
+      </c>
+      <c r="B81" s="101" t="s">
+        <v>288</v>
+      </c>
+      <c r="C81" s="103">
+        <f ca="1"/>
+        <v>118265350</v>
+      </c>
+      <c r="D81" s="103">
+        <f ca="1"/>
+        <v>108435542</v>
+      </c>
+      <c r="E81" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.3582209152180424E-4</v>
+      </c>
+      <c r="F81" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.0300213839772337E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="102" t="s">
+        <v>299</v>
+      </c>
+      <c r="B82" s="102" t="s">
+        <v>300</v>
+      </c>
+      <c r="C82" s="103">
+        <f ca="1"/>
+        <v>140275689</v>
+      </c>
+      <c r="D82" s="103">
+        <f ca="1"/>
+        <v>101433842</v>
+      </c>
+      <c r="E82" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.109987740869512E-3</v>
+      </c>
+      <c r="F82" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.4469514831121337E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="101" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83" s="101" t="s">
+        <v>68</v>
+      </c>
+      <c r="C83" s="103">
+        <f ca="1"/>
+        <v>123045872</v>
+      </c>
+      <c r="D83" s="103">
+        <f ca="1"/>
+        <v>100910325</v>
+      </c>
+      <c r="E83" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.7364989228175634E-4</v>
+      </c>
+      <c r="F83" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.4033553557014769E-4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="102" t="s">
+        <v>144</v>
+      </c>
+      <c r="B84" s="102" t="s">
+        <v>145</v>
+      </c>
+      <c r="C84" s="103">
+        <f ca="1"/>
+        <v>96388846</v>
+      </c>
+      <c r="D84" s="103">
+        <f ca="1"/>
+        <v>100254242</v>
+      </c>
+      <c r="E84" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.627154653758949E-4</v>
+      </c>
+      <c r="F84" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.3487197315288786E-4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="101" t="s">
+        <v>254</v>
+      </c>
+      <c r="B85" s="101" t="s">
+        <v>255</v>
+      </c>
+      <c r="C85" s="103">
+        <f ca="1"/>
+        <v>90567038</v>
+      </c>
+      <c r="D85" s="103">
+        <f ca="1"/>
+        <v>98997841</v>
+      </c>
+      <c r="E85" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.1664807083473496E-4</v>
+      </c>
+      <c r="F85" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.2440923401072509E-4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="102" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="102" t="s">
+        <v>91</v>
+      </c>
+      <c r="C86" s="103">
+        <f ca="1"/>
+        <v>70046989</v>
+      </c>
+      <c r="D86" s="103">
+        <f ca="1"/>
+        <v>98312485</v>
+      </c>
+      <c r="E86" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.5427493979246509E-4</v>
+      </c>
+      <c r="F86" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.187018992923381E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="101" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" s="101" t="s">
+        <v>212</v>
+      </c>
+      <c r="C87" s="103">
+        <f ca="1"/>
+        <v>76457410</v>
+      </c>
+      <c r="D87" s="103">
+        <f ca="1"/>
+        <v>97867400</v>
+      </c>
+      <c r="E87" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.0499997115418935E-4</v>
+      </c>
+      <c r="F87" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.1499543276525831E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="102" t="s">
+        <v>290</v>
+      </c>
+      <c r="B88" s="102" t="s">
+        <v>291</v>
+      </c>
+      <c r="C88" s="103">
+        <f ca="1"/>
+        <v>85471621</v>
+      </c>
+      <c r="D88" s="103">
+        <f ca="1"/>
+        <v>97660795</v>
+      </c>
+      <c r="E88" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.7632853688742278E-4</v>
+      </c>
+      <c r="F88" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.1327491979172001E-4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="101" t="s">
+        <v>278</v>
+      </c>
+      <c r="B89" s="101" t="s">
+        <v>279</v>
+      </c>
+      <c r="C89" s="103">
+        <f ca="1"/>
+        <v>121713827</v>
+      </c>
+      <c r="D89" s="103">
+        <f ca="1"/>
+        <v>96737872</v>
+      </c>
+      <c r="E89" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.6310955110912066E-4</v>
+      </c>
+      <c r="F89" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.0558923457075768E-4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="102" t="s">
+        <v>155</v>
+      </c>
+      <c r="B90" s="102" t="s">
+        <v>156</v>
+      </c>
+      <c r="C90" s="103">
+        <f ca="1"/>
+        <v>72268053</v>
+      </c>
+      <c r="D90" s="103">
+        <f ca="1"/>
+        <v>95879390</v>
+      </c>
+      <c r="E90" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.7185000093999303E-4</v>
+      </c>
+      <c r="F90" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.9844018484519859E-4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="101" t="s">
+        <v>308</v>
+      </c>
+      <c r="B91" s="101" t="s">
+        <v>309</v>
+      </c>
+      <c r="C91" s="103">
+        <f ca="1"/>
+        <v>58625389</v>
+      </c>
+      <c r="D91" s="103">
+        <f ca="1"/>
+        <v>95091701</v>
+      </c>
+      <c r="E91" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.6389694149858243E-4</v>
+      </c>
+      <c r="F91" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.9188066719744824E-4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="102" t="s">
+        <v>302</v>
+      </c>
+      <c r="B92" s="102" t="s">
+        <v>303</v>
+      </c>
+      <c r="C92" s="103">
+        <f ca="1"/>
+        <v>76520582</v>
+      </c>
+      <c r="D92" s="103">
+        <f ca="1"/>
+        <v>92792908</v>
+      </c>
+      <c r="E92" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.0549984498169346E-4</v>
+      </c>
+      <c r="F92" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.7273735904915023E-4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="101" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" s="103">
+        <f ca="1"/>
+        <v>94189915</v>
+      </c>
+      <c r="D93" s="103">
+        <f ca="1"/>
+        <v>91870998</v>
+      </c>
+      <c r="E93" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.4531554048215271E-4</v>
+      </c>
+      <c r="F93" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.6506010963391471E-4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="102" t="s">
+        <v>223</v>
+      </c>
+      <c r="B94" s="102" t="s">
+        <v>224</v>
+      </c>
+      <c r="C94" s="103">
+        <f ca="1"/>
+        <v>76974150</v>
+      </c>
+      <c r="D94" s="103">
+        <f ca="1"/>
+        <v>89716963</v>
+      </c>
+      <c r="E94" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.0908888398937718E-4</v>
+      </c>
+      <c r="F94" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.4712228062224671E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="101" t="s">
+        <v>412</v>
+      </c>
+      <c r="B95" s="101" t="s">
+        <v>413</v>
+      </c>
+      <c r="C95" s="103">
+        <f ca="1"/>
+        <v>123594163</v>
+      </c>
+      <c r="D95" s="103">
+        <f ca="1"/>
+        <v>80774272</v>
+      </c>
+      <c r="E95" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.7798846507913596E-4</v>
+      </c>
+      <c r="F95" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.7265159557665464E-4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="102" t="s">
+        <v>120</v>
+      </c>
+      <c r="B96" s="102" t="s">
+        <v>121</v>
+      </c>
+      <c r="C96" s="103">
+        <f ca="1"/>
+        <v>88519478</v>
+      </c>
+      <c r="D96" s="103">
+        <f ca="1"/>
+        <v>79424657</v>
+      </c>
+      <c r="E96" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.0044592978736663E-4</v>
+      </c>
+      <c r="F96" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.614126124117654E-4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="101" t="s">
+        <v>457</v>
+      </c>
+      <c r="B97" s="101" t="s">
+        <v>458</v>
+      </c>
+      <c r="C97" s="103">
+        <f ca="1"/>
+        <v>43658058</v>
+      </c>
+      <c r="D97" s="103">
+        <f ca="1"/>
+        <v>71871307</v>
+      </c>
+      <c r="E97" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.4546192227343203E-4</v>
+      </c>
+      <c r="F97" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.9851173068733554E-4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="102" t="s">
+        <v>327</v>
+      </c>
+      <c r="B98" s="102" t="s">
+        <v>328</v>
+      </c>
+      <c r="C98" s="103">
+        <f ca="1"/>
+        <v>32189294</v>
+      </c>
+      <c r="D98" s="103">
+        <f ca="1"/>
+        <v>66380661</v>
+      </c>
+      <c r="E98" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.5471071988279124E-4</v>
+      </c>
+      <c r="F98" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.5278811472399291E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="101" t="s">
+        <v>235</v>
+      </c>
+      <c r="B99" s="101" t="s">
+        <v>236</v>
+      </c>
+      <c r="C99" s="103">
+        <f ca="1"/>
+        <v>49618244</v>
+      </c>
+      <c r="D99" s="103">
+        <f ca="1"/>
+        <v>65435333</v>
+      </c>
+      <c r="E99" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.9262428832890795E-4</v>
+      </c>
+      <c r="F99" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.4491585079887469E-4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="C100" s="103">
+        <f ca="1"/>
+        <v>54778278</v>
+      </c>
+      <c r="D100" s="103">
+        <f ca="1"/>
+        <v>63226323</v>
+      </c>
+      <c r="E100" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.3345513024671079E-4</v>
+      </c>
+      <c r="F100" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.2652021485746032E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="101" t="s">
+        <v>329</v>
+      </c>
+      <c r="B101" s="101" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101" s="103">
+        <f ca="1"/>
+        <v>44477669</v>
+      </c>
+      <c r="D101" s="103">
+        <f ca="1"/>
+        <v>62834380</v>
+      </c>
+      <c r="E101" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.5194742356568949E-4</v>
+      </c>
+      <c r="F101" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.2325629086536168E-4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="C102" s="103">
+        <f ca="1"/>
+        <v>117039377</v>
+      </c>
+      <c r="D102" s="103">
+        <f ca="1"/>
+        <v>61946135</v>
+      </c>
+      <c r="E102" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.2612108766049357E-4</v>
+      </c>
+      <c r="F102" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.1585938834034742E-4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="101" t="s">
+        <v>390</v>
+      </c>
+      <c r="B103" s="101" t="s">
+        <v>391</v>
+      </c>
+      <c r="C103" s="103">
+        <f ca="1"/>
+        <v>30156451</v>
+      </c>
+      <c r="D103" s="103">
+        <f ca="1"/>
+        <v>60151576</v>
+      </c>
+      <c r="E103" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.3862503301004737E-4</v>
+      </c>
+      <c r="F103" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.0091511283259114E-4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="102" t="s">
+        <v>432</v>
+      </c>
+      <c r="B104" s="102" t="s">
+        <v>433</v>
+      </c>
+      <c r="C104" s="103">
+        <f ca="1"/>
+        <v>65005138</v>
+      </c>
+      <c r="D104" s="103">
+        <f ca="1"/>
+        <v>60000000</v>
+      </c>
+      <c r="E104" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.1437926833872735E-4</v>
+      </c>
+      <c r="F104" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.9965285647637003E-4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="101" t="s">
+        <v>501</v>
+      </c>
+      <c r="B105" s="101" t="s">
+        <v>502</v>
+      </c>
+      <c r="C105" s="103">
+        <f ca="1"/>
+        <v>50505064</v>
+      </c>
+      <c r="D105" s="103">
+        <f ca="1"/>
+        <v>59598242</v>
+      </c>
+      <c r="E105" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.9964160783291622E-4</v>
+      </c>
+      <c r="F105" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.9630719760449947E-4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="102" t="s">
+        <v>435</v>
+      </c>
+      <c r="B106" s="102" t="s">
+        <v>436</v>
+      </c>
+      <c r="C106" s="103">
+        <f ca="1"/>
+        <v>94267375</v>
+      </c>
+      <c r="D106" s="103">
+        <f ca="1"/>
+        <v>54154503</v>
+      </c>
+      <c r="E106" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.4592847384944317E-4</v>
+      </c>
+      <c r="F106" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.5097420191680254E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="101" t="s">
+        <v>363</v>
+      </c>
+      <c r="B107" s="101" t="s">
+        <v>364</v>
+      </c>
+      <c r="C107" s="103">
+        <f ca="1"/>
+        <v>51338387</v>
+      </c>
+      <c r="D107" s="103">
+        <f ca="1"/>
+        <v>54144995</v>
+      </c>
+      <c r="E107" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.062356108335688E-4</v>
+      </c>
+      <c r="F107" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.5089502359414626E-4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="102" t="s">
+        <v>348</v>
+      </c>
+      <c r="B108" s="102" t="s">
+        <v>349</v>
+      </c>
+      <c r="C108" s="103">
+        <f ca="1"/>
+        <v>60784898</v>
+      </c>
+      <c r="D108" s="103">
+        <f ca="1"/>
+        <v>48669232</v>
+      </c>
+      <c r="E108" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.8098492398068862E-4</v>
+      </c>
+      <c r="F108" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.0529534652185262E-4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="101" t="s">
+        <v>454</v>
+      </c>
+      <c r="B109" s="101" t="s">
+        <v>455</v>
+      </c>
+      <c r="C109" s="103">
+        <f ca="1"/>
+        <v>16496484</v>
+      </c>
+      <c r="D109" s="103">
+        <f ca="1"/>
+        <v>48174641</v>
+      </c>
+      <c r="E109" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.3053505663016243E-4</v>
+      </c>
+      <c r="F109" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.0117661642289422E-4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="102" t="s">
+        <v>471</v>
+      </c>
+      <c r="B110" s="102" t="s">
+        <v>472</v>
+      </c>
+      <c r="C110" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D110" s="103">
+        <f ca="1"/>
+        <v>45938730</v>
+      </c>
+      <c r="E110" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.8255696112327861E-4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="101" t="s">
+        <v>158</v>
+      </c>
+      <c r="B111" s="101" t="s">
+        <v>159</v>
+      </c>
+      <c r="C111" s="103">
+        <f ca="1"/>
+        <v>36579494</v>
+      </c>
+      <c r="D111" s="103">
+        <f ca="1"/>
+        <v>44856636</v>
+      </c>
+      <c r="E111" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.8944994101729111E-4</v>
+      </c>
+      <c r="F111" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.7354577182201291E-4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="102" t="s">
+        <v>426</v>
+      </c>
+      <c r="B112" s="102" t="s">
+        <v>427</v>
+      </c>
+      <c r="C112" s="103">
+        <f ca="1"/>
+        <v>51075759</v>
+      </c>
+      <c r="D112" s="103">
+        <f ca="1"/>
+        <v>44093954</v>
+      </c>
+      <c r="E112" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.0415746128044785E-4</v>
+      </c>
+      <c r="F112" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.6719450115729442E-4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="101" t="s">
+        <v>663</v>
+      </c>
+      <c r="B113" s="101" t="s">
+        <v>664</v>
+      </c>
+      <c r="C113" s="103">
+        <f ca="1"/>
+        <v>44718116</v>
+      </c>
+      <c r="D113" s="103">
+        <f ca="1"/>
+        <v>42020072</v>
+      </c>
+      <c r="E113" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.5385005704574211E-4</v>
+      </c>
+      <c r="F113" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.4992415006904562E-4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="102" t="s">
+        <v>429</v>
+      </c>
+      <c r="B114" s="102" t="s">
+        <v>430</v>
+      </c>
+      <c r="C114" s="103">
+        <f ca="1"/>
+        <v>44123278</v>
+      </c>
+      <c r="D114" s="103">
+        <f ca="1"/>
+        <v>41800145</v>
+      </c>
+      <c r="E114" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.4914316241196609E-4</v>
+      </c>
+      <c r="F114" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.480926975062743E-4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="B115" s="101" t="s">
+        <v>130</v>
+      </c>
+      <c r="C115" s="103">
+        <f ca="1"/>
+        <v>37728580</v>
+      </c>
+      <c r="D115" s="103">
+        <f ca="1"/>
+        <v>30307256</v>
+      </c>
+      <c r="E115" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.9854254560399737E-4</v>
+      </c>
+      <c r="F115" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.5238511720601008E-4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="B116" s="102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C116" s="103">
+        <f ca="1"/>
+        <v>26721546</v>
+      </c>
+      <c r="D116" s="103">
+        <f ca="1"/>
+        <v>30251837</v>
+      </c>
+      <c r="E116" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.1144496732488513E-4</v>
+      </c>
+      <c r="F116" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.519236128451257E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="101" t="s">
+        <v>257</v>
+      </c>
+      <c r="B117" s="101" t="s">
+        <v>258</v>
+      </c>
+      <c r="C117" s="103">
+        <f ca="1"/>
+        <v>150000000</v>
+      </c>
+      <c r="D117" s="103">
+        <f ca="1"/>
+        <v>30000000</v>
+      </c>
+      <c r="E117" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1869352581146604E-3</v>
+      </c>
+      <c r="F117" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.4982642823818501E-4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="102" t="s">
+        <v>399</v>
+      </c>
+      <c r="B118" s="102" t="s">
+        <v>400</v>
+      </c>
+      <c r="C118" s="103">
+        <f ca="1"/>
+        <v>36590568</v>
+      </c>
+      <c r="D118" s="103">
+        <f ca="1"/>
+        <v>27447829</v>
+      </c>
+      <c r="E118" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.8953756849094684E-4</v>
+      </c>
+      <c r="F118" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.2857310273208248E-4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="101" t="s">
+        <v>166</v>
+      </c>
+      <c r="B119" s="101" t="s">
+        <v>167</v>
+      </c>
+      <c r="C119" s="103">
+        <f ca="1"/>
+        <v>31824228</v>
+      </c>
+      <c r="D119" s="103">
+        <f ca="1"/>
+        <v>24153517</v>
+      </c>
+      <c r="E119" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.5182198850319868E-4</v>
+      </c>
+      <c r="F119" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>2.0113956271667607E-4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="102" t="s">
+        <v>335</v>
+      </c>
+      <c r="B120" s="102" t="s">
+        <v>336</v>
+      </c>
+      <c r="C120" s="103">
+        <f ca="1"/>
+        <v>16728240</v>
+      </c>
+      <c r="D120" s="103">
+        <f ca="1"/>
+        <v>23461305</v>
+      </c>
+      <c r="E120" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.323689190813599E-4</v>
+      </c>
+      <c r="F120" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.9537513433188906E-4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="101" t="s">
+        <v>296</v>
+      </c>
+      <c r="B121" s="101" t="s">
+        <v>297</v>
+      </c>
+      <c r="C121" s="103">
+        <f ca="1"/>
+        <v>21521675</v>
+      </c>
+      <c r="D121" s="103">
+        <f ca="1"/>
+        <v>22947408</v>
+      </c>
+      <c r="E121" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.7029889914123221E-4</v>
+      </c>
+      <c r="F121" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.9109563259881178E-4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="102" t="s">
+        <v>440</v>
+      </c>
+      <c r="B122" s="102" t="s">
+        <v>441</v>
+      </c>
+      <c r="C122" s="103">
+        <f ca="1"/>
+        <v>41680000</v>
+      </c>
+      <c r="D122" s="103">
+        <f ca="1"/>
+        <v>20000000</v>
+      </c>
+      <c r="E122" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.2980974372146026E-4</v>
+      </c>
+      <c r="F122" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.6655095215879003E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="101" t="s">
+        <v>340</v>
+      </c>
+      <c r="B123" s="101" t="s">
+        <v>341</v>
+      </c>
+      <c r="C123" s="103">
+        <f ca="1"/>
+        <v>22045194</v>
+      </c>
+      <c r="D123" s="103">
+        <f ca="1"/>
+        <v>19896212</v>
+      </c>
+      <c r="E123" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.7444145353718505E-4</v>
+      </c>
+      <c r="F123" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.656866526476572E-4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="102" t="s">
+        <v>489</v>
+      </c>
+      <c r="B124" s="102" t="s">
+        <v>490</v>
+      </c>
+      <c r="C124" s="103">
+        <f ca="1"/>
+        <v>14746190</v>
+      </c>
+      <c r="D124" s="103">
+        <f ca="1"/>
+        <v>19158874</v>
+      </c>
+      <c r="E124" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1668515222571882E-4</v>
+      </c>
+      <c r="F124" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.595464353495143E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="101" t="s">
+        <v>404</v>
+      </c>
+      <c r="B125" s="101" t="s">
+        <v>405</v>
+      </c>
+      <c r="C125" s="103">
+        <f ca="1"/>
+        <v>10393404</v>
+      </c>
+      <c r="D125" s="103">
+        <f ca="1"/>
+        <v>15115102</v>
+      </c>
+      <c r="E125" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.224198439619962E-5</v>
+      </c>
+      <c r="F125" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2587173150386158E-4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="102" t="s">
+        <v>149</v>
+      </c>
+      <c r="B126" s="102" t="s">
+        <v>150</v>
+      </c>
+      <c r="C126" s="103">
+        <f ca="1"/>
+        <v>11672267</v>
+      </c>
+      <c r="D126" s="103">
+        <f ca="1"/>
+        <v>13548838</v>
+      </c>
+      <c r="E126" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.2361501629521537E-5</v>
+      </c>
+      <c r="F126" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1282859347725982E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="101" t="s">
+        <v>169</v>
+      </c>
+      <c r="B127" s="101" t="s">
+        <v>170</v>
+      </c>
+      <c r="C127" s="103">
+        <f ca="1"/>
+        <v>11825559</v>
+      </c>
+      <c r="D127" s="103">
+        <f ca="1"/>
+        <v>11985970</v>
+      </c>
+      <c r="E127" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.3574486160100955E-5</v>
+      </c>
+      <c r="F127" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.9813735802334631E-5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="102" t="s">
+        <v>485</v>
+      </c>
+      <c r="B128" s="102" t="s">
+        <v>483</v>
+      </c>
+      <c r="C128" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D128" s="103">
+        <f ca="1"/>
+        <v>11019918</v>
+      </c>
+      <c r="E128" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F128" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.1768891780589457E-5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="101" t="s">
+        <v>321</v>
+      </c>
+      <c r="B129" s="101" t="s">
+        <v>322</v>
+      </c>
+      <c r="C129" s="103">
+        <f ca="1"/>
+        <v>6499171</v>
+      </c>
+      <c r="D129" s="103">
+        <f ca="1"/>
+        <v>10057678</v>
+      </c>
+      <c r="E129" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>5.1427301389442097E-5</v>
+      </c>
+      <c r="F129" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>8.3755792370325752E-5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="102" t="s">
+        <v>443</v>
+      </c>
+      <c r="B130" s="102" t="s">
+        <v>444</v>
+      </c>
+      <c r="C130" s="103">
+        <f ca="1"/>
+        <v>3791602</v>
+      </c>
+      <c r="D130" s="103">
+        <f ca="1"/>
+        <v>8955659</v>
+      </c>
+      <c r="E130" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>3.0002573990253746E-5</v>
+      </c>
+      <c r="F130" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>7.4578676682971867E-5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="101" t="s">
+        <v>446</v>
+      </c>
+      <c r="B131" s="101" t="s">
+        <v>447</v>
+      </c>
+      <c r="C131" s="103">
+        <f ca="1"/>
+        <v>7597091</v>
+      </c>
+      <c r="D131" s="103">
+        <f ca="1"/>
+        <v>8222294</v>
+      </c>
+      <c r="E131" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.0115034446703752E-5</v>
+      </c>
+      <c r="F131" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.8471544731475316E-5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="102" t="s">
+        <v>438</v>
+      </c>
+      <c r="B132" s="102" t="s">
+        <v>439</v>
+      </c>
+      <c r="C132" s="103">
+        <f ca="1"/>
+        <v>5541341</v>
+      </c>
+      <c r="D132" s="103">
+        <f ca="1"/>
+        <v>8109643</v>
+      </c>
+      <c r="E132" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>4.3848086734242331E-5</v>
+      </c>
+      <c r="F132" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.7533438165893317E-5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="101" t="s">
+        <v>465</v>
+      </c>
+      <c r="B133" s="101" t="s">
+        <v>466</v>
+      </c>
+      <c r="C133" s="103">
+        <f ca="1"/>
+        <v>12607915</v>
+      </c>
+      <c r="D133" s="103">
+        <f ca="1"/>
+        <v>7796035</v>
+      </c>
+      <c r="E133" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>9.9765192298751309E-5</v>
+      </c>
+      <c r="F133" s="104">
+        <f t="shared" ca="1" si="1"/>
+        <v>6.4921852615662626E-5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="102" t="s">
+        <v>415</v>
+      </c>
+      <c r="B134" s="102" t="s">
+        <v>416</v>
+      </c>
+      <c r="C134" s="103">
+        <f ca="1"/>
+        <v>5490297</v>
+      </c>
+      <c r="D134" s="103">
+        <f ca="1"/>
+        <v>5499855</v>
+      </c>
+      <c r="E134" s="104">
+        <f t="shared" ref="E134:F147" ca="1" si="2">C134/C$149</f>
+        <v>4.344418057880763E-5</v>
+      </c>
+      <c r="F134" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>4.5800304349264109E-5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="101" t="s">
+        <v>409</v>
+      </c>
+      <c r="B135" s="101" t="s">
+        <v>410</v>
+      </c>
+      <c r="C135" s="103">
+        <f ca="1"/>
+        <v>922978</v>
+      </c>
+      <c r="D135" s="103">
+        <f ca="1"/>
+        <v>4835634</v>
+      </c>
+      <c r="E135" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>7.3034342044276858E-6</v>
+      </c>
+      <c r="F135" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>4.0268972349570924E-5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="B136" s="102" t="s">
+        <v>325</v>
+      </c>
+      <c r="C136" s="103">
+        <f ca="1"/>
+        <v>4033122</v>
+      </c>
+      <c r="D136" s="103">
+        <f ca="1"/>
+        <v>3754947</v>
+      </c>
+      <c r="E136" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>3.1913698013852763E-5</v>
+      </c>
+      <c r="F136" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>3.1269499907789604E-5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B137" s="101" t="s">
+        <v>103</v>
+      </c>
+      <c r="C137" s="103">
+        <f ca="1"/>
+        <v>3447159</v>
+      </c>
+      <c r="D137" s="103">
+        <f ca="1"/>
+        <v>3604096</v>
+      </c>
+      <c r="E137" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>2.7277030382848493E-5</v>
+      </c>
+      <c r="F137" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>3.0013281023584325E-5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="102" t="s">
+        <v>238</v>
+      </c>
+      <c r="B138" s="102" t="s">
+        <v>239</v>
+      </c>
+      <c r="C138" s="103">
+        <f ca="1"/>
+        <v>711128</v>
+      </c>
+      <c r="D138" s="103">
+        <f ca="1"/>
+        <v>738278</v>
+      </c>
+      <c r="E138" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>5.6270859748837476E-6</v>
+      </c>
+      <c r="F138" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>6.1480451928943591E-6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="B139" s="101" t="s">
+        <v>248</v>
+      </c>
+      <c r="C139" s="103">
+        <f ca="1"/>
+        <v>407084</v>
+      </c>
+      <c r="D139" s="103">
+        <f ca="1"/>
+        <v>674911</v>
+      </c>
+      <c r="E139" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>3.2212156840956558E-6</v>
+      </c>
+      <c r="F139" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>5.6203534836220571E-6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="102" t="s">
+        <v>23</v>
+      </c>
+      <c r="B140" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D140" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E140" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="101" t="s">
+        <v>195</v>
+      </c>
+      <c r="B141" s="101" t="s">
+        <v>196</v>
+      </c>
+      <c r="C141" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D141" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E141" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F141" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="102" t="s">
+        <v>311</v>
+      </c>
+      <c r="B142" s="102" t="s">
+        <v>312</v>
+      </c>
+      <c r="C142" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D142" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E142" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F142" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="101" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="101" t="s">
+        <v>317</v>
+      </c>
+      <c r="C143" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D143" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E143" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F143" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="102" t="s">
+        <v>402</v>
+      </c>
+      <c r="B144" s="102" t="s">
+        <v>403</v>
+      </c>
+      <c r="C144" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D144" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E144" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F144" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="101" t="s">
+        <v>407</v>
+      </c>
+      <c r="B145" s="101" t="s">
+        <v>408</v>
+      </c>
+      <c r="C145" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D145" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E145" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="102" t="s">
+        <v>468</v>
+      </c>
+      <c r="B146" s="102" t="s">
+        <v>469</v>
+      </c>
+      <c r="C146" s="103">
+        <f ca="1"/>
+        <v>45622476</v>
+      </c>
+      <c r="D146" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E146" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>3.610061688459326E-4</v>
+      </c>
+      <c r="F146" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="101" t="s">
+        <v>482</v>
+      </c>
+      <c r="B147" s="101" t="s">
+        <v>483</v>
+      </c>
+      <c r="C147" s="103">
+        <f ca="1"/>
+        <v>17780909</v>
+      </c>
+      <c r="D147" s="103">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E147" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>1.4069858542285524E-4</v>
+      </c>
+      <c r="F147" s="104">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B149" s="43" t="s">
+        <v>3099</v>
+      </c>
+      <c r="C149" s="104">
+        <f ca="1">SUM(C5:C147)</f>
+        <v>126375890323</v>
+      </c>
+      <c r="D149" s="104">
+        <f ca="1">SUM(D5:D147)</f>
+        <v>120083372330</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C5:C147">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{933AABCB-7312-4FD0-AB11-9E5B7CD74148}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D147">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{48DE66B4-1DC5-4FD8-97BB-042DA34C609F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{933AABCB-7312-4FD0-AB11-9E5B7CD74148}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C5:C147</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{48DE66B4-1DC5-4FD8-97BB-042DA34C609F}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D5:D147</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB1E745-1F5B-4B52-986E-D369F3C3E6AE}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C20"/>
